--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\05 - WorkedHourPointing\01 - LP's\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF2E108-C878-48AC-9A05-EECC54F6DD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7903534F-A14D-49EA-8C5D-D61EDAD29A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
   <si>
     <t>LPs</t>
   </si>
@@ -34,103 +34,100 @@
     <t>Line already used!</t>
   </si>
   <si>
-    <t>LP051629</t>
-  </si>
-  <si>
-    <t>LP051627</t>
-  </si>
-  <si>
-    <t>LP051626</t>
-  </si>
-  <si>
-    <t>LP051618</t>
-  </si>
-  <si>
-    <t>LP051617</t>
-  </si>
-  <si>
-    <t>LP051609</t>
-  </si>
-  <si>
-    <t>LP051608</t>
-  </si>
-  <si>
-    <t>LP051607</t>
-  </si>
-  <si>
-    <t>LP051606</t>
-  </si>
-  <si>
-    <t>LP051605</t>
-  </si>
-  <si>
-    <t>LP051604</t>
-  </si>
-  <si>
-    <t>LP051603</t>
-  </si>
-  <si>
-    <t>LP051602</t>
-  </si>
-  <si>
-    <t>LP051601</t>
-  </si>
-  <si>
-    <t>LP051600</t>
-  </si>
-  <si>
-    <t>LP051599</t>
-  </si>
-  <si>
-    <t>LP051598</t>
-  </si>
-  <si>
-    <t>LP051575</t>
-  </si>
-  <si>
-    <t>LP051570</t>
-  </si>
-  <si>
-    <t>LP051537</t>
-  </si>
-  <si>
-    <t>LP051507</t>
-  </si>
-  <si>
-    <t>LP051506</t>
-  </si>
-  <si>
-    <t>LP051502</t>
-  </si>
-  <si>
-    <t>LP051501</t>
-  </si>
-  <si>
-    <t>LP051500</t>
-  </si>
-  <si>
-    <t>LP051498</t>
-  </si>
-  <si>
-    <t>LP051497</t>
-  </si>
-  <si>
-    <t>LP051496</t>
-  </si>
-  <si>
-    <t>LP051495</t>
-  </si>
-  <si>
-    <t>LP051494</t>
-  </si>
-  <si>
-    <t>LP051409</t>
-  </si>
-  <si>
-    <t>LP051375</t>
-  </si>
-  <si>
-    <t>LP051320</t>
+    <t>LP052500</t>
+  </si>
+  <si>
+    <t>LP052502</t>
+  </si>
+  <si>
+    <t>LP052503</t>
+  </si>
+  <si>
+    <t>LP052492</t>
+  </si>
+  <si>
+    <t>LP052488</t>
+  </si>
+  <si>
+    <t>LP052498</t>
+  </si>
+  <si>
+    <t>LP052497</t>
+  </si>
+  <si>
+    <t>LP052499</t>
+  </si>
+  <si>
+    <t>LP052496</t>
+  </si>
+  <si>
+    <t>LP052558</t>
+  </si>
+  <si>
+    <t>LP052573</t>
+  </si>
+  <si>
+    <t>LP052570</t>
+  </si>
+  <si>
+    <t>LP052571</t>
+  </si>
+  <si>
+    <t>LP052569</t>
+  </si>
+  <si>
+    <t>LP052563</t>
+  </si>
+  <si>
+    <t>LP052539</t>
+  </si>
+  <si>
+    <t>LP052538</t>
+  </si>
+  <si>
+    <t>LP052668</t>
+  </si>
+  <si>
+    <t>LP052567</t>
+  </si>
+  <si>
+    <t>LP052565</t>
+  </si>
+  <si>
+    <t>LP052602</t>
+  </si>
+  <si>
+    <t>LP052588</t>
+  </si>
+  <si>
+    <t>LP052532</t>
+  </si>
+  <si>
+    <t>LP052593</t>
+  </si>
+  <si>
+    <t>LP052591</t>
+  </si>
+  <si>
+    <t>LP052590</t>
+  </si>
+  <si>
+    <t>LP052592</t>
+  </si>
+  <si>
+    <t>LP052667</t>
+  </si>
+  <si>
+    <t>LP052630</t>
+  </si>
+  <si>
+    <t>LP052693</t>
+  </si>
+  <si>
+    <t>LP052659</t>
+  </si>
+  <si>
+    <t>LP052640</t>
   </si>
 </sst>
 </file>
@@ -149,6 +146,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -493,9 +491,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -763,14 +762,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7903534F-A14D-49EA-8C5D-D61EDAD29A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D594584-BFA8-4D30-8851-54A99A1D116A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>LPs</t>
   </si>
@@ -31,103 +31,277 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Line already used!</t>
-  </si>
-  <si>
-    <t>LP052500</t>
-  </si>
-  <si>
-    <t>LP052502</t>
-  </si>
-  <si>
-    <t>LP052503</t>
-  </si>
-  <si>
-    <t>LP052492</t>
-  </si>
-  <si>
-    <t>LP052488</t>
-  </si>
-  <si>
-    <t>LP052498</t>
-  </si>
-  <si>
-    <t>LP052497</t>
-  </si>
-  <si>
-    <t>LP052499</t>
-  </si>
-  <si>
-    <t>LP052496</t>
-  </si>
-  <si>
-    <t>LP052558</t>
-  </si>
-  <si>
-    <t>LP052573</t>
-  </si>
-  <si>
-    <t>LP052570</t>
-  </si>
-  <si>
-    <t>LP052571</t>
-  </si>
-  <si>
-    <t>LP052569</t>
-  </si>
-  <si>
-    <t>LP052563</t>
-  </si>
-  <si>
-    <t>LP052539</t>
-  </si>
-  <si>
-    <t>LP052538</t>
-  </si>
-  <si>
-    <t>LP052668</t>
-  </si>
-  <si>
-    <t>LP052567</t>
-  </si>
-  <si>
-    <t>LP052565</t>
-  </si>
-  <si>
-    <t>LP052602</t>
-  </si>
-  <si>
-    <t>LP052588</t>
-  </si>
-  <si>
-    <t>LP052532</t>
-  </si>
-  <si>
-    <t>LP052593</t>
-  </si>
-  <si>
-    <t>LP052591</t>
-  </si>
-  <si>
-    <t>LP052590</t>
-  </si>
-  <si>
-    <t>LP052592</t>
-  </si>
-  <si>
-    <t>LP052667</t>
-  </si>
-  <si>
-    <t>LP052630</t>
-  </si>
-  <si>
-    <t>LP052693</t>
-  </si>
-  <si>
-    <t>LP052659</t>
-  </si>
-  <si>
-    <t>LP052640</t>
+    <t>LP052665</t>
+  </si>
+  <si>
+    <t>LP052660</t>
+  </si>
+  <si>
+    <t>LP052657</t>
+  </si>
+  <si>
+    <t>LP052648</t>
+  </si>
+  <si>
+    <t>LP052757</t>
+  </si>
+  <si>
+    <t>LP052763</t>
+  </si>
+  <si>
+    <t>LP052776</t>
+  </si>
+  <si>
+    <t>LP052922</t>
+  </si>
+  <si>
+    <t>LP052857</t>
+  </si>
+  <si>
+    <t>LP052761</t>
+  </si>
+  <si>
+    <t>LP052846</t>
+  </si>
+  <si>
+    <t>LP052845</t>
+  </si>
+  <si>
+    <t>LP052811</t>
+  </si>
+  <si>
+    <t>LP052810</t>
+  </si>
+  <si>
+    <t>LP052849</t>
+  </si>
+  <si>
+    <t>LP052853</t>
+  </si>
+  <si>
+    <t>LP052847</t>
+  </si>
+  <si>
+    <t>LP052854</t>
+  </si>
+  <si>
+    <t>LP052851</t>
+  </si>
+  <si>
+    <t>LP052850</t>
+  </si>
+  <si>
+    <t>LP052840</t>
+  </si>
+  <si>
+    <t>LP052852</t>
+  </si>
+  <si>
+    <t>LP052835</t>
+  </si>
+  <si>
+    <t>LP052886</t>
+  </si>
+  <si>
+    <t>LP052834</t>
+  </si>
+  <si>
+    <t>LP052832</t>
+  </si>
+  <si>
+    <t>LP052884</t>
+  </si>
+  <si>
+    <t>LP052831</t>
+  </si>
+  <si>
+    <t>LP052887</t>
+  </si>
+  <si>
+    <t>LP053041</t>
+  </si>
+  <si>
+    <t>LP053042</t>
+  </si>
+  <si>
+    <t>LP052888</t>
+  </si>
+  <si>
+    <t>LP053148</t>
+  </si>
+  <si>
+    <t>LP052966</t>
+  </si>
+  <si>
+    <t>LP052968</t>
+  </si>
+  <si>
+    <t>LP052969</t>
+  </si>
+  <si>
+    <t>LP052971</t>
+  </si>
+  <si>
+    <t>LP052975</t>
+  </si>
+  <si>
+    <t>LP052974</t>
+  </si>
+  <si>
+    <t>LP052951</t>
+  </si>
+  <si>
+    <t>LP052955</t>
+  </si>
+  <si>
+    <t>LP052953</t>
+  </si>
+  <si>
+    <t>LP052954</t>
+  </si>
+  <si>
+    <t>LP052931</t>
+  </si>
+  <si>
+    <t>LP052998</t>
+  </si>
+  <si>
+    <t>LP052981</t>
+  </si>
+  <si>
+    <t>LP053016</t>
+  </si>
+  <si>
+    <t>LP053152</t>
+  </si>
+  <si>
+    <t>LP052948</t>
+  </si>
+  <si>
+    <t>LP053190</t>
+  </si>
+  <si>
+    <t>LP053135</t>
+  </si>
+  <si>
+    <t>LP053129</t>
+  </si>
+  <si>
+    <t>LP053140</t>
+  </si>
+  <si>
+    <t>LP053144</t>
+  </si>
+  <si>
+    <t>LP053141</t>
+  </si>
+  <si>
+    <t>LP053192</t>
+  </si>
+  <si>
+    <t>LP053164</t>
+  </si>
+  <si>
+    <t>LP053161</t>
+  </si>
+  <si>
+    <t>LP053171</t>
+  </si>
+  <si>
+    <t>LP053193</t>
+  </si>
+  <si>
+    <t>LP053194</t>
+  </si>
+  <si>
+    <t>LP053189</t>
+  </si>
+  <si>
+    <t>LP053196</t>
+  </si>
+  <si>
+    <t>LP053195</t>
+  </si>
+  <si>
+    <t>LP053197</t>
+  </si>
+  <si>
+    <t>LP053198</t>
+  </si>
+  <si>
+    <t>LP053855</t>
+  </si>
+  <si>
+    <t>LP053745</t>
+  </si>
+  <si>
+    <t>LP053270</t>
+  </si>
+  <si>
+    <t>LP053271</t>
+  </si>
+  <si>
+    <t>LP053272</t>
+  </si>
+  <si>
+    <t>LP053334</t>
+  </si>
+  <si>
+    <t>LP053285</t>
+  </si>
+  <si>
+    <t>LP053332</t>
+  </si>
+  <si>
+    <t>LP053284</t>
+  </si>
+  <si>
+    <t>LP053288</t>
+  </si>
+  <si>
+    <t>LP053287</t>
+  </si>
+  <si>
+    <t>LP053290</t>
+  </si>
+  <si>
+    <t>LP053283</t>
+  </si>
+  <si>
+    <t>LP053381</t>
+  </si>
+  <si>
+    <t>LP053350</t>
+  </si>
+  <si>
+    <t>LP053324</t>
+  </si>
+  <si>
+    <t>LP053474</t>
+  </si>
+  <si>
+    <t>LP053475</t>
+  </si>
+  <si>
+    <t>LP053356</t>
+  </si>
+  <si>
+    <t>LP053387</t>
+  </si>
+  <si>
+    <t>LP054121</t>
+  </si>
+  <si>
+    <t>LP053357</t>
+  </si>
+  <si>
+    <t>LP053359</t>
+  </si>
+  <si>
+    <t>LP053355</t>
+  </si>
+  <si>
+    <t>LP053354</t>
   </si>
 </sst>
 </file>
@@ -491,11 +665,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -508,258 +682,457 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B25" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B30" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B31" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B32" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B33" t="s">
-        <v>2</v>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7903534F-A14D-49EA-8C5D-D61EDAD29A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B258E588-4BDA-4FA5-86FA-26CA72321621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>LPs</t>
   </si>
@@ -31,103 +31,277 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Line already used!</t>
-  </si>
-  <si>
-    <t>LP052500</t>
-  </si>
-  <si>
-    <t>LP052502</t>
-  </si>
-  <si>
-    <t>LP052503</t>
-  </si>
-  <si>
-    <t>LP052492</t>
-  </si>
-  <si>
-    <t>LP052488</t>
-  </si>
-  <si>
-    <t>LP052498</t>
-  </si>
-  <si>
-    <t>LP052497</t>
-  </si>
-  <si>
-    <t>LP052499</t>
-  </si>
-  <si>
-    <t>LP052496</t>
-  </si>
-  <si>
-    <t>LP052558</t>
-  </si>
-  <si>
-    <t>LP052573</t>
-  </si>
-  <si>
-    <t>LP052570</t>
-  </si>
-  <si>
-    <t>LP052571</t>
-  </si>
-  <si>
-    <t>LP052569</t>
-  </si>
-  <si>
-    <t>LP052563</t>
-  </si>
-  <si>
-    <t>LP052539</t>
-  </si>
-  <si>
-    <t>LP052538</t>
-  </si>
-  <si>
-    <t>LP052668</t>
-  </si>
-  <si>
-    <t>LP052567</t>
-  </si>
-  <si>
-    <t>LP052565</t>
-  </si>
-  <si>
-    <t>LP052602</t>
-  </si>
-  <si>
-    <t>LP052588</t>
-  </si>
-  <si>
-    <t>LP052532</t>
-  </si>
-  <si>
-    <t>LP052593</t>
-  </si>
-  <si>
-    <t>LP052591</t>
-  </si>
-  <si>
-    <t>LP052590</t>
-  </si>
-  <si>
-    <t>LP052592</t>
-  </si>
-  <si>
-    <t>LP052667</t>
-  </si>
-  <si>
-    <t>LP052630</t>
-  </si>
-  <si>
-    <t>LP052693</t>
-  </si>
-  <si>
-    <t>LP052659</t>
-  </si>
-  <si>
-    <t>LP052640</t>
+    <t>LP052665</t>
+  </si>
+  <si>
+    <t>LP052660</t>
+  </si>
+  <si>
+    <t>LP052657</t>
+  </si>
+  <si>
+    <t>LP052648</t>
+  </si>
+  <si>
+    <t>LP052757</t>
+  </si>
+  <si>
+    <t>LP052763</t>
+  </si>
+  <si>
+    <t>LP052776</t>
+  </si>
+  <si>
+    <t>LP052922</t>
+  </si>
+  <si>
+    <t>LP052857</t>
+  </si>
+  <si>
+    <t>LP052761</t>
+  </si>
+  <si>
+    <t>LP052846</t>
+  </si>
+  <si>
+    <t>LP052845</t>
+  </si>
+  <si>
+    <t>LP052811</t>
+  </si>
+  <si>
+    <t>LP052810</t>
+  </si>
+  <si>
+    <t>LP052849</t>
+  </si>
+  <si>
+    <t>LP052853</t>
+  </si>
+  <si>
+    <t>LP052847</t>
+  </si>
+  <si>
+    <t>LP052854</t>
+  </si>
+  <si>
+    <t>LP052851</t>
+  </si>
+  <si>
+    <t>LP052850</t>
+  </si>
+  <si>
+    <t>LP052840</t>
+  </si>
+  <si>
+    <t>LP052852</t>
+  </si>
+  <si>
+    <t>LP052835</t>
+  </si>
+  <si>
+    <t>LP052886</t>
+  </si>
+  <si>
+    <t>LP052834</t>
+  </si>
+  <si>
+    <t>LP052832</t>
+  </si>
+  <si>
+    <t>LP052884</t>
+  </si>
+  <si>
+    <t>LP052831</t>
+  </si>
+  <si>
+    <t>LP052887</t>
+  </si>
+  <si>
+    <t>LP053041</t>
+  </si>
+  <si>
+    <t>LP053042</t>
+  </si>
+  <si>
+    <t>LP052888</t>
+  </si>
+  <si>
+    <t>LP053148</t>
+  </si>
+  <si>
+    <t>LP052966</t>
+  </si>
+  <si>
+    <t>LP052968</t>
+  </si>
+  <si>
+    <t>LP052969</t>
+  </si>
+  <si>
+    <t>LP052971</t>
+  </si>
+  <si>
+    <t>LP052975</t>
+  </si>
+  <si>
+    <t>LP052974</t>
+  </si>
+  <si>
+    <t>LP052951</t>
+  </si>
+  <si>
+    <t>LP052955</t>
+  </si>
+  <si>
+    <t>LP052953</t>
+  </si>
+  <si>
+    <t>LP052954</t>
+  </si>
+  <si>
+    <t>LP052931</t>
+  </si>
+  <si>
+    <t>LP052998</t>
+  </si>
+  <si>
+    <t>LP052981</t>
+  </si>
+  <si>
+    <t>LP053016</t>
+  </si>
+  <si>
+    <t>LP053152</t>
+  </si>
+  <si>
+    <t>LP052948</t>
+  </si>
+  <si>
+    <t>LP053190</t>
+  </si>
+  <si>
+    <t>LP053135</t>
+  </si>
+  <si>
+    <t>LP053129</t>
+  </si>
+  <si>
+    <t>LP053140</t>
+  </si>
+  <si>
+    <t>LP053144</t>
+  </si>
+  <si>
+    <t>LP053141</t>
+  </si>
+  <si>
+    <t>LP053192</t>
+  </si>
+  <si>
+    <t>LP053164</t>
+  </si>
+  <si>
+    <t>LP053161</t>
+  </si>
+  <si>
+    <t>LP053171</t>
+  </si>
+  <si>
+    <t>LP053193</t>
+  </si>
+  <si>
+    <t>LP053194</t>
+  </si>
+  <si>
+    <t>LP053189</t>
+  </si>
+  <si>
+    <t>LP053196</t>
+  </si>
+  <si>
+    <t>LP053195</t>
+  </si>
+  <si>
+    <t>LP053197</t>
+  </si>
+  <si>
+    <t>LP053198</t>
+  </si>
+  <si>
+    <t>LP053855</t>
+  </si>
+  <si>
+    <t>LP053745</t>
+  </si>
+  <si>
+    <t>LP053270</t>
+  </si>
+  <si>
+    <t>LP053271</t>
+  </si>
+  <si>
+    <t>LP053272</t>
+  </si>
+  <si>
+    <t>LP053334</t>
+  </si>
+  <si>
+    <t>LP053285</t>
+  </si>
+  <si>
+    <t>LP053332</t>
+  </si>
+  <si>
+    <t>LP053284</t>
+  </si>
+  <si>
+    <t>LP053288</t>
+  </si>
+  <si>
+    <t>LP053287</t>
+  </si>
+  <si>
+    <t>LP053290</t>
+  </si>
+  <si>
+    <t>LP053283</t>
+  </si>
+  <si>
+    <t>LP053381</t>
+  </si>
+  <si>
+    <t>LP053350</t>
+  </si>
+  <si>
+    <t>LP053324</t>
+  </si>
+  <si>
+    <t>LP053474</t>
+  </si>
+  <si>
+    <t>LP053475</t>
+  </si>
+  <si>
+    <t>LP053356</t>
+  </si>
+  <si>
+    <t>LP053387</t>
+  </si>
+  <si>
+    <t>LP054121</t>
+  </si>
+  <si>
+    <t>LP053357</t>
+  </si>
+  <si>
+    <t>LP053359</t>
+  </si>
+  <si>
+    <t>LP053355</t>
+  </si>
+  <si>
+    <t>LP053354</t>
   </si>
 </sst>
 </file>
@@ -491,11 +665,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -508,258 +682,457 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B25" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B30" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B31" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B32" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B33" t="s">
-        <v>2</v>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B258E588-4BDA-4FA5-86FA-26CA72321621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E604B1-7151-4B56-A480-1BDB0156F6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="94">
   <si>
     <t>LPs</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>LP053354</t>
+  </si>
+  <si>
+    <t>LP already have pointing!</t>
   </si>
 </sst>
 </file>
@@ -669,7 +672,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -684,55 +687,88 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
+      <c r="B6" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
+      <c r="B7" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E604B1-7151-4B56-A480-1BDB0156F6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6BF7B9-7925-453C-B0A6-F279611E93DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$33</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="95">
   <si>
     <t>LPs</t>
   </si>
@@ -34,6 +31,9 @@
     <t>LP052665</t>
   </si>
   <si>
+    <t>LP already have pointing!</t>
+  </si>
+  <si>
     <t>LP052660</t>
   </si>
   <si>
@@ -73,6 +73,9 @@
     <t>LP052810</t>
   </si>
   <si>
+    <t>Apointing created!</t>
+  </si>
+  <si>
     <t>LP052849</t>
   </si>
   <si>
@@ -302,9 +305,6 @@
   </si>
   <si>
     <t>LP053354</t>
-  </si>
-  <si>
-    <t>LP already have pointing!</t>
   </si>
 </sst>
 </file>
@@ -323,7 +323,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -688,487 +687,691 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="B67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="B68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="B69" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="B70" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="B71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="B72" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7497C9-D02E-42AC-A2B8-3FB38397EA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23216F84-4349-413D-9BB5-547855B0DEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="88">
   <si>
     <t>LPs</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>LP054118</t>
+  </si>
+  <si>
+    <t>Apointing created!</t>
   </si>
   <si>
     <t>LP054069</t>
@@ -645,10 +648,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -662,425 +661,629 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="B52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="B56" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="B58" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="B60" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="B61" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="B63" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="B66" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="B67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="B68" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LP054469</t>
+          <t>LP056783</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LP054485</t>
+          <t>LP056784</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LP054486</t>
+          <t>LP056786</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LP054423</t>
+          <t>LP056785</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LP054422</t>
+          <t>LP055517</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LP054690</t>
+          <t>LP055536</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LP054691</t>
+          <t>LP055540</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LP054692</t>
+          <t>LP055556</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LP054693</t>
+          <t>LP055554</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LP054694</t>
+          <t>LP055553</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LP054695</t>
+          <t>LP055555</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LP054696</t>
+          <t>LP055552</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LP054466</t>
+          <t>LP055537</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LP054510</t>
+          <t>LP055546</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LP054511</t>
+          <t>LP055551</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LP054509</t>
+          <t>LP055550</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LP054484</t>
+          <t>LP055549</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -643,6 +643,318 @@
           <t>Apointing created!</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LP055544</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LP055545</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LP055543</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LP055535</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LP055575</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LP055576</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LP055530</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LP055531</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LP055629</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LP055630</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LP055625</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LP055626</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LP055627</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LP055570</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LP055622</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LP055638</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LP055571</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LP055572</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LP055569</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LP055620</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LP055581</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LP055619</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LP055621</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LP055623</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LP055580</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LP055618</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LP055617</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LP055589</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LP055600</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LP055628</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LP055687</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LP055742</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LP055598</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>LP055599</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LP056783</t>
+          <t>LP055593</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LP056784</t>
+          <t>LP055594</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LP056786</t>
+          <t>LP055917</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LP056785</t>
+          <t>LP055603</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LP055517</t>
+          <t>LP055720</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LP055536</t>
+          <t>LP055777</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LP055540</t>
+          <t>LP055721</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LP055556</t>
+          <t>LP055606</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LP055554</t>
+          <t>LP055527</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LP055553</t>
+          <t>LP055607</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LP055555</t>
+          <t>LP055688</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LP055552</t>
+          <t>LP055592</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LP055537</t>
+          <t>LP055875</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LP055546</t>
+          <t>LP055741</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LP055551</t>
+          <t>LP055865</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LP055550</t>
+          <t>LP055936</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LP055549</t>
+          <t>LP056792</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LP055544</t>
+          <t>LP056791</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LP055545</t>
+          <t>LP055771</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LP055543</t>
+          <t>LP056787</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LP055535</t>
+          <t>LP055601</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LP055575</t>
+          <t>LP055602</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LP055576</t>
+          <t>LP055604</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LP055530</t>
+          <t>LP055918</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LP055531</t>
+          <t>LP055904</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LP055629</t>
+          <t>LP055911</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LP055630</t>
+          <t>LP055928</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -767,71 +767,103 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LP055625</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>LP055906</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LP055626</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>LP055907</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LP055627</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>LP055908</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LP055570</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>LP055909</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LP055622</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>LP055910</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LP055638</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>LP055941</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LP055571</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>LP056079</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LP055572</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>LP055957</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LP055569</t>
+          <t>LP055955</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -839,7 +871,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LP055620</t>
+          <t>LP056601</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -847,7 +879,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LP055581</t>
+          <t>LP056078</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -855,7 +887,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LP055619</t>
+          <t>LP056076</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -863,7 +895,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LP055621</t>
+          <t>LP056077</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -871,7 +903,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LP055623</t>
+          <t>LP056728</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -879,7 +911,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LP055580</t>
+          <t>LP056793</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -887,7 +919,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LP055618</t>
+          <t>LP056074</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -895,7 +927,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LP055617</t>
+          <t>LP056073</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -903,7 +935,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LP055589</t>
+          <t>LP056075</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -911,7 +943,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LP055600</t>
+          <t>LP056016</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -919,7 +951,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LP055628</t>
+          <t>LP056794</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -927,7 +959,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LP055687</t>
+          <t>LP056795</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -935,7 +967,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LP055742</t>
+          <t>LP056796</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -943,7 +975,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LP055598</t>
+          <t>LP056797</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -951,10 +983,946 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LP055599</t>
+          <t>LP056072</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LP056071</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>LP056070</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>LP056546</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>LP056798</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LP056799</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>LP056068</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>LP056229</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LP056065</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LP056602</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LP056157</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>LP056101</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>LP056112</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LP056114</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LP056110</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LP056111</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LP056100</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LP056146</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>LP056155</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>LP056156</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LP056159</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>LP056158</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>LP056102</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>LP056169</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>LP056145</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>LP056800</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>LP056801</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LP056181</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>LP056270</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>LP056271</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>LP056175</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>LP056176</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>LP056180</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>LP056182</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>LP056183</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>LP056177</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>LP056171</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>LP056172</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>LP056173</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>LP056174</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>LP056179</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>LP056214</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>LP056215</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>LP056216</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>LP056559</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>LP056272</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>LP056264</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>LP056254</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>LP056251</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>LP056269</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>LP056256</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>LP056255</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>LP056258</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>LP056253</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>LP056290</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>LP056242</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LP056243</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>LP056252</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>LP056260</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>LP056297</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>LP056259</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>LP056240</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>LP056261</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>LP056241</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>LP056313</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>LP056309</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>LP056370</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>LP056342</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>LP056340</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>LP056426</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>LP056345</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>LP056460</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>LP056427</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>LP056425</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>LP056343</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>LP056341</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>LP056344</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>LP056802</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>LP056267</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>LP056268</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>LP056450</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>LP056347</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>LP056314</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>LP056445</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>LP056417</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>LP056418</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>LP056419</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>LP056416</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>LP056331</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>LP056315</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>LP057297</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>LP057298</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>LP056338</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>LP056444</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>LP056429</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>LP056430</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>LP056431</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>LP056432</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>LP056433</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>LP056434</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>LP056435</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>LP056436</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>LP056437</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>LP056461</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>LP056458</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>LP056428</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>LP056514</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>LP056448</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>LP056449</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>LP056447</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>LP056551</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>LP056570</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>LP056572</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>LP056573</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>LP056569</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>LP056568</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>LP056734</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>LP056707</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -866,7 +866,11 @@
           <t>LP055955</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -874,7 +878,11 @@
           <t>LP056601</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -882,7 +890,11 @@
           <t>LP056078</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -890,7 +902,11 @@
           <t>LP056076</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -898,7 +914,11 @@
           <t>LP056077</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -906,7 +926,11 @@
           <t>LP056728</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -914,7 +938,11 @@
           <t>LP056793</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -922,7 +950,11 @@
           <t>LP056074</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -930,7 +962,11 @@
           <t>LP056073</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -938,7 +974,11 @@
           <t>LP056075</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -946,7 +986,11 @@
           <t>LP056016</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -954,7 +998,11 @@
           <t>LP056794</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -962,7 +1010,11 @@
           <t>LP056795</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -970,7 +1022,11 @@
           <t>LP056796</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -978,7 +1034,11 @@
           <t>LP056797</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -986,7 +1046,11 @@
           <t>LP056072</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -994,7 +1058,11 @@
           <t>LP056071</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1002,7 +1070,11 @@
           <t>LP056070</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1010,7 +1082,11 @@
           <t>LP056546</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1018,7 +1094,11 @@
           <t>LP056798</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1026,7 +1106,11 @@
           <t>LP056799</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1034,7 +1118,11 @@
           <t>LP056068</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1042,7 +1130,11 @@
           <t>LP056229</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1050,7 +1142,11 @@
           <t>LP056065</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1058,7 +1154,11 @@
           <t>LP056602</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1066,7 +1166,11 @@
           <t>LP056157</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1074,7 +1178,11 @@
           <t>LP056101</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1082,7 +1190,11 @@
           <t>LP056112</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1090,7 +1202,11 @@
           <t>LP056114</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1098,7 +1214,11 @@
           <t>LP056110</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1106,7 +1226,11 @@
           <t>LP056111</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1114,7 +1238,11 @@
           <t>LP056100</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1122,7 +1250,11 @@
           <t>LP056146</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -1262,7 +1262,11 @@
           <t>LP056155</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1270,7 +1274,11 @@
           <t>LP056156</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -1,37 +1,417 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76117FB3-9D40-47BB-92C7-0B03DE251D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+  <si>
+    <t>LPs</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>LP056735</t>
+  </si>
+  <si>
+    <t>LP056594</t>
+  </si>
+  <si>
+    <t>LP056704</t>
+  </si>
+  <si>
+    <t>LP056705</t>
+  </si>
+  <si>
+    <t>LP056706</t>
+  </si>
+  <si>
+    <t>LP056732</t>
+  </si>
+  <si>
+    <t>LP056583</t>
+  </si>
+  <si>
+    <t>LP056733</t>
+  </si>
+  <si>
+    <t>LP056710</t>
+  </si>
+  <si>
+    <t>LP056711</t>
+  </si>
+  <si>
+    <t>LP056864</t>
+  </si>
+  <si>
+    <t>LP056724</t>
+  </si>
+  <si>
+    <t>LP056723</t>
+  </si>
+  <si>
+    <t>LP056766</t>
+  </si>
+  <si>
+    <t>LP056764</t>
+  </si>
+  <si>
+    <t>LP056765</t>
+  </si>
+  <si>
+    <t>LP056745</t>
+  </si>
+  <si>
+    <t>LP056725</t>
+  </si>
+  <si>
+    <t>LP056862</t>
+  </si>
+  <si>
+    <t>LP056863</t>
+  </si>
+  <si>
+    <t>LP057295</t>
+  </si>
+  <si>
+    <t>LP056888</t>
+  </si>
+  <si>
+    <t>LP056893</t>
+  </si>
+  <si>
+    <t>LP056875</t>
+  </si>
+  <si>
+    <t>LP056930</t>
+  </si>
+  <si>
+    <t>LP056927</t>
+  </si>
+  <si>
+    <t>LP056921</t>
+  </si>
+  <si>
+    <t>LP056931</t>
+  </si>
+  <si>
+    <t>LP056926</t>
+  </si>
+  <si>
+    <t>LP056937</t>
+  </si>
+  <si>
+    <t>LP056925</t>
+  </si>
+  <si>
+    <t>LP056915</t>
+  </si>
+  <si>
+    <t>LP056916</t>
+  </si>
+  <si>
+    <t>LP056940</t>
+  </si>
+  <si>
+    <t>LP056922</t>
+  </si>
+  <si>
+    <t>LP056929</t>
+  </si>
+  <si>
+    <t>LP056924</t>
+  </si>
+  <si>
+    <t>LP056923</t>
+  </si>
+  <si>
+    <t>LP056928</t>
+  </si>
+  <si>
+    <t>LP056939</t>
+  </si>
+  <si>
+    <t>LP056938</t>
+  </si>
+  <si>
+    <t>LP056914</t>
+  </si>
+  <si>
+    <t>LP057012</t>
+  </si>
+  <si>
+    <t>LP057045</t>
+  </si>
+  <si>
+    <t>LP058219</t>
+  </si>
+  <si>
+    <t>LP058220</t>
+  </si>
+  <si>
+    <t>LP056956</t>
+  </si>
+  <si>
+    <t>LP057018</t>
+  </si>
+  <si>
+    <t>LP056955</t>
+  </si>
+  <si>
+    <t>LP057026</t>
+  </si>
+  <si>
+    <t>LP057109</t>
+  </si>
+  <si>
+    <t>LP057102</t>
+  </si>
+  <si>
+    <t>LP057110</t>
+  </si>
+  <si>
+    <t>LP057576</t>
+  </si>
+  <si>
+    <t>LP057577</t>
+  </si>
+  <si>
+    <t>LP057088</t>
+  </si>
+  <si>
+    <t>LP057104</t>
+  </si>
+  <si>
+    <t>LP057105</t>
+  </si>
+  <si>
+    <t>LP057103</t>
+  </si>
+  <si>
+    <t>LP057106</t>
+  </si>
+  <si>
+    <t>LP057107</t>
+  </si>
+  <si>
+    <t>LP057108</t>
+  </si>
+  <si>
+    <t>LP057063</t>
+  </si>
+  <si>
+    <t>LP057090</t>
+  </si>
+  <si>
+    <t>LP057100</t>
+  </si>
+  <si>
+    <t>LP057096</t>
+  </si>
+  <si>
+    <t>LP057097</t>
+  </si>
+  <si>
+    <t>LP057439</t>
+  </si>
+  <si>
+    <t>LP057150</t>
+  </si>
+  <si>
+    <t>LP057151</t>
+  </si>
+  <si>
+    <t>LP057286</t>
+  </si>
+  <si>
+    <t>LP057098</t>
+  </si>
+  <si>
+    <t>LP057099</t>
+  </si>
+  <si>
+    <t>LP057101</t>
+  </si>
+  <si>
+    <t>LP057113</t>
+  </si>
+  <si>
+    <t>LP058309</t>
+  </si>
+  <si>
+    <t>LP057081</t>
+  </si>
+  <si>
+    <t>LP057152</t>
+  </si>
+  <si>
+    <t>LP057287</t>
+  </si>
+  <si>
+    <t>LP057153</t>
+  </si>
+  <si>
+    <t>LP057118</t>
+  </si>
+  <si>
+    <t>LP057139</t>
+  </si>
+  <si>
+    <t>LP057124</t>
+  </si>
+  <si>
+    <t>LP057131</t>
+  </si>
+  <si>
+    <t>LP057154</t>
+  </si>
+  <si>
+    <t>LP057136</t>
+  </si>
+  <si>
+    <t>LP057122</t>
+  </si>
+  <si>
+    <t>LP057123</t>
+  </si>
+  <si>
+    <t>LP057138</t>
+  </si>
+  <si>
+    <t>LP057233</t>
+  </si>
+  <si>
+    <t>LP057172</t>
+  </si>
+  <si>
+    <t>LP057173</t>
+  </si>
+  <si>
+    <t>LP057175</t>
+  </si>
+  <si>
+    <t>LP057186</t>
+  </si>
+  <si>
+    <t>LP057163</t>
+  </si>
+  <si>
+    <t>LP057210</t>
+  </si>
+  <si>
+    <t>LP057212</t>
+  </si>
+  <si>
+    <t>LP057211</t>
+  </si>
+  <si>
+    <t>LP057208</t>
+  </si>
+  <si>
+    <t>LP057177</t>
+  </si>
+  <si>
+    <t>LP057180</t>
+  </si>
+  <si>
+    <t>LP057179</t>
+  </si>
+  <si>
+    <t>LP057405</t>
+  </si>
+  <si>
+    <t>LP057392</t>
+  </si>
+  <si>
+    <t>LP057391</t>
+  </si>
+  <si>
+    <t>LP057196</t>
+  </si>
+  <si>
+    <t>LP057293</t>
+  </si>
+  <si>
+    <t>LP057206</t>
+  </si>
+  <si>
+    <t>LP057205</t>
+  </si>
+  <si>
+    <t>LP057292</t>
+  </si>
+  <si>
+    <t>LP057207</t>
+  </si>
+  <si>
+    <t>LP057393</t>
+  </si>
+  <si>
+    <t>LP057482</t>
+  </si>
+  <si>
+    <t>LP057227</t>
+  </si>
+  <si>
+    <t>LP057229</t>
+  </si>
+  <si>
+    <t>LP057230</t>
+  </si>
+  <si>
+    <t>LP057231</t>
+  </si>
+  <si>
+    <t>LP057232</t>
+  </si>
+  <si>
+    <t>LP057316</t>
+  </si>
+  <si>
+    <t>LP057384</t>
+  </si>
+  <si>
+    <t>LP057304</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +426,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,36 +750,621 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B122"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LPs</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LP056707</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Apointing created!</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEC6742-4E4E-46FE-A744-5CBFD251BD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7FA8FC-E9DB-4E82-9067-F5FEF5FD9D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,383 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="189">
   <si>
     <t>LPs</t>
   </si>
   <si>
+    <t>Hour</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
+    <t>LP056735</t>
+  </si>
+  <si>
+    <t>Apointing created!</t>
+  </si>
+  <si>
+    <t>LP056594</t>
+  </si>
+  <si>
+    <t>LP056704</t>
+  </si>
+  <si>
+    <t>LP056705</t>
+  </si>
+  <si>
+    <t>LP056706</t>
+  </si>
+  <si>
+    <t>LP056732</t>
+  </si>
+  <si>
+    <t>LP056583</t>
+  </si>
+  <si>
+    <t>LP056733</t>
+  </si>
+  <si>
+    <t>LP056710</t>
+  </si>
+  <si>
+    <t>LP056711</t>
+  </si>
+  <si>
+    <t>LP056864</t>
+  </si>
+  <si>
+    <t>LP056724</t>
+  </si>
+  <si>
+    <t>LP056723</t>
+  </si>
+  <si>
+    <t>LP056766</t>
+  </si>
+  <si>
+    <t>LP056764</t>
+  </si>
+  <si>
+    <t>LP056765</t>
+  </si>
+  <si>
+    <t>LP056745</t>
+  </si>
+  <si>
+    <t>LP056725</t>
+  </si>
+  <si>
+    <t>LP056862</t>
+  </si>
+  <si>
+    <t>LP056863</t>
+  </si>
+  <si>
+    <t>LP057295</t>
+  </si>
+  <si>
+    <t>LP056888</t>
+  </si>
+  <si>
+    <t>LP056893</t>
+  </si>
+  <si>
+    <t>LP056875</t>
+  </si>
+  <si>
+    <t>LP056930</t>
+  </si>
+  <si>
+    <t>LP056927</t>
+  </si>
+  <si>
+    <t>LP056921</t>
+  </si>
+  <si>
+    <t>LP056931</t>
+  </si>
+  <si>
+    <t>LP056926</t>
+  </si>
+  <si>
+    <t>LP056937</t>
+  </si>
+  <si>
+    <t>LP056925</t>
+  </si>
+  <si>
+    <t>LP056915</t>
+  </si>
+  <si>
+    <t>LP056916</t>
+  </si>
+  <si>
+    <t>LP056940</t>
+  </si>
+  <si>
+    <t>LP056922</t>
+  </si>
+  <si>
+    <t>LP056929</t>
+  </si>
+  <si>
+    <t>LP056924</t>
+  </si>
+  <si>
+    <t>LP056923</t>
+  </si>
+  <si>
+    <t>LP056928</t>
+  </si>
+  <si>
+    <t>LP056939</t>
+  </si>
+  <si>
+    <t>LP056938</t>
+  </si>
+  <si>
+    <t>LP056914</t>
+  </si>
+  <si>
+    <t>LP057012</t>
+  </si>
+  <si>
+    <t>LP057045</t>
+  </si>
+  <si>
+    <t>LP058219</t>
+  </si>
+  <si>
+    <t>LP058220</t>
+  </si>
+  <si>
+    <t>LP056956</t>
+  </si>
+  <si>
+    <t>LP057018</t>
+  </si>
+  <si>
+    <t>LP056955</t>
+  </si>
+  <si>
+    <t>LP057026</t>
+  </si>
+  <si>
+    <t>LP057109</t>
+  </si>
+  <si>
+    <t>LP057102</t>
+  </si>
+  <si>
+    <t>LP057110</t>
+  </si>
+  <si>
+    <t>LP057576</t>
+  </si>
+  <si>
+    <t>LP057577</t>
+  </si>
+  <si>
+    <t>LP057088</t>
+  </si>
+  <si>
+    <t>LP057104</t>
+  </si>
+  <si>
+    <t>LP057105</t>
+  </si>
+  <si>
+    <t>LP057103</t>
+  </si>
+  <si>
+    <t>LP057106</t>
+  </si>
+  <si>
+    <t>LP057107</t>
+  </si>
+  <si>
+    <t>LP057108</t>
+  </si>
+  <si>
+    <t>LP057063</t>
+  </si>
+  <si>
+    <t>LP057090</t>
+  </si>
+  <si>
+    <t>LP057100</t>
+  </si>
+  <si>
+    <t>LP057096</t>
+  </si>
+  <si>
+    <t>LP057097</t>
+  </si>
+  <si>
+    <t>LP057439</t>
+  </si>
+  <si>
+    <t>LP057150</t>
+  </si>
+  <si>
+    <t>LP057151</t>
+  </si>
+  <si>
+    <t>LP057286</t>
+  </si>
+  <si>
+    <t>LP057098</t>
+  </si>
+  <si>
+    <t>LP057099</t>
+  </si>
+  <si>
+    <t>LP057101</t>
+  </si>
+  <si>
+    <t>LP057113</t>
+  </si>
+  <si>
+    <t>LP058309</t>
+  </si>
+  <si>
+    <t>LP057081</t>
+  </si>
+  <si>
+    <t>LP057152</t>
+  </si>
+  <si>
+    <t>LP057287</t>
+  </si>
+  <si>
+    <t>LP057153</t>
+  </si>
+  <si>
+    <t>LP057118</t>
+  </si>
+  <si>
+    <t>LP057139</t>
+  </si>
+  <si>
+    <t>LP057124</t>
+  </si>
+  <si>
+    <t>LP057131</t>
+  </si>
+  <si>
+    <t>LP057154</t>
+  </si>
+  <si>
+    <t>LP057136</t>
+  </si>
+  <si>
+    <t>LP057122</t>
+  </si>
+  <si>
+    <t>LP057123</t>
+  </si>
+  <si>
+    <t>LP057138</t>
+  </si>
+  <si>
+    <t>LP057233</t>
+  </si>
+  <si>
+    <t>LP057172</t>
+  </si>
+  <si>
+    <t>LP057173</t>
+  </si>
+  <si>
+    <t>LP057175</t>
+  </si>
+  <si>
+    <t>LP057186</t>
+  </si>
+  <si>
+    <t>LP057163</t>
+  </si>
+  <si>
+    <t>LP057210</t>
+  </si>
+  <si>
+    <t>LP057212</t>
+  </si>
+  <si>
+    <t>LP057211</t>
+  </si>
+  <si>
+    <t>LP057208</t>
+  </si>
+  <si>
+    <t>LP057177</t>
+  </si>
+  <si>
+    <t>LP057180</t>
+  </si>
+  <si>
+    <t>LP057179</t>
+  </si>
+  <si>
+    <t>LP057405</t>
+  </si>
+  <si>
+    <t>LP057392</t>
+  </si>
+  <si>
+    <t>LP057391</t>
+  </si>
+  <si>
+    <t>LP057196</t>
+  </si>
+  <si>
+    <t>LP057293</t>
+  </si>
+  <si>
+    <t>LP057206</t>
+  </si>
+  <si>
+    <t>LP057205</t>
+  </si>
+  <si>
+    <t>LP057292</t>
+  </si>
+  <si>
+    <t>LP057207</t>
+  </si>
+  <si>
+    <t>LP057393</t>
+  </si>
+  <si>
+    <t>LP057482</t>
+  </si>
+  <si>
+    <t>LP057227</t>
+  </si>
+  <si>
+    <t>LP057229</t>
+  </si>
+  <si>
+    <t>LP057230</t>
+  </si>
+  <si>
+    <t>LP057231</t>
+  </si>
+  <si>
+    <t>LP057232</t>
+  </si>
+  <si>
+    <t>LP057316</t>
+  </si>
+  <si>
+    <t>LP057384</t>
+  </si>
+  <si>
+    <t>LP057304</t>
+  </si>
+  <si>
     <t>LP057596</t>
   </si>
   <si>
@@ -218,372 +587,6 @@
   </si>
   <si>
     <t>LP057556</t>
-  </si>
-  <si>
-    <t>Hour</t>
-  </si>
-  <si>
-    <t>LP056735</t>
-  </si>
-  <si>
-    <t>LP056594</t>
-  </si>
-  <si>
-    <t>LP056704</t>
-  </si>
-  <si>
-    <t>LP056705</t>
-  </si>
-  <si>
-    <t>LP056706</t>
-  </si>
-  <si>
-    <t>LP056732</t>
-  </si>
-  <si>
-    <t>LP056583</t>
-  </si>
-  <si>
-    <t>LP056733</t>
-  </si>
-  <si>
-    <t>LP056710</t>
-  </si>
-  <si>
-    <t>LP056711</t>
-  </si>
-  <si>
-    <t>LP056864</t>
-  </si>
-  <si>
-    <t>LP056724</t>
-  </si>
-  <si>
-    <t>LP056723</t>
-  </si>
-  <si>
-    <t>LP056766</t>
-  </si>
-  <si>
-    <t>LP056764</t>
-  </si>
-  <si>
-    <t>LP056765</t>
-  </si>
-  <si>
-    <t>LP056745</t>
-  </si>
-  <si>
-    <t>LP056725</t>
-  </si>
-  <si>
-    <t>LP056862</t>
-  </si>
-  <si>
-    <t>LP056863</t>
-  </si>
-  <si>
-    <t>LP057295</t>
-  </si>
-  <si>
-    <t>LP056888</t>
-  </si>
-  <si>
-    <t>LP056893</t>
-  </si>
-  <si>
-    <t>LP056875</t>
-  </si>
-  <si>
-    <t>LP056930</t>
-  </si>
-  <si>
-    <t>LP056927</t>
-  </si>
-  <si>
-    <t>LP056921</t>
-  </si>
-  <si>
-    <t>LP056931</t>
-  </si>
-  <si>
-    <t>LP056926</t>
-  </si>
-  <si>
-    <t>LP056937</t>
-  </si>
-  <si>
-    <t>LP056925</t>
-  </si>
-  <si>
-    <t>LP056915</t>
-  </si>
-  <si>
-    <t>LP056916</t>
-  </si>
-  <si>
-    <t>LP056940</t>
-  </si>
-  <si>
-    <t>LP056922</t>
-  </si>
-  <si>
-    <t>LP056929</t>
-  </si>
-  <si>
-    <t>LP056924</t>
-  </si>
-  <si>
-    <t>LP056923</t>
-  </si>
-  <si>
-    <t>LP056928</t>
-  </si>
-  <si>
-    <t>LP056939</t>
-  </si>
-  <si>
-    <t>LP056938</t>
-  </si>
-  <si>
-    <t>LP056914</t>
-  </si>
-  <si>
-    <t>LP057012</t>
-  </si>
-  <si>
-    <t>LP057045</t>
-  </si>
-  <si>
-    <t>LP058219</t>
-  </si>
-  <si>
-    <t>LP058220</t>
-  </si>
-  <si>
-    <t>LP056956</t>
-  </si>
-  <si>
-    <t>LP057018</t>
-  </si>
-  <si>
-    <t>LP056955</t>
-  </si>
-  <si>
-    <t>LP057026</t>
-  </si>
-  <si>
-    <t>LP057109</t>
-  </si>
-  <si>
-    <t>LP057102</t>
-  </si>
-  <si>
-    <t>LP057110</t>
-  </si>
-  <si>
-    <t>LP057576</t>
-  </si>
-  <si>
-    <t>LP057577</t>
-  </si>
-  <si>
-    <t>LP057088</t>
-  </si>
-  <si>
-    <t>LP057104</t>
-  </si>
-  <si>
-    <t>LP057105</t>
-  </si>
-  <si>
-    <t>LP057103</t>
-  </si>
-  <si>
-    <t>LP057106</t>
-  </si>
-  <si>
-    <t>LP057107</t>
-  </si>
-  <si>
-    <t>LP057108</t>
-  </si>
-  <si>
-    <t>LP057063</t>
-  </si>
-  <si>
-    <t>LP057090</t>
-  </si>
-  <si>
-    <t>LP057100</t>
-  </si>
-  <si>
-    <t>LP057096</t>
-  </si>
-  <si>
-    <t>LP057097</t>
-  </si>
-  <si>
-    <t>LP057439</t>
-  </si>
-  <si>
-    <t>LP057150</t>
-  </si>
-  <si>
-    <t>LP057151</t>
-  </si>
-  <si>
-    <t>LP057286</t>
-  </si>
-  <si>
-    <t>LP057098</t>
-  </si>
-  <si>
-    <t>LP057099</t>
-  </si>
-  <si>
-    <t>LP057101</t>
-  </si>
-  <si>
-    <t>LP057113</t>
-  </si>
-  <si>
-    <t>LP058309</t>
-  </si>
-  <si>
-    <t>LP057081</t>
-  </si>
-  <si>
-    <t>LP057152</t>
-  </si>
-  <si>
-    <t>LP057287</t>
-  </si>
-  <si>
-    <t>LP057153</t>
-  </si>
-  <si>
-    <t>LP057118</t>
-  </si>
-  <si>
-    <t>LP057139</t>
-  </si>
-  <si>
-    <t>LP057124</t>
-  </si>
-  <si>
-    <t>LP057131</t>
-  </si>
-  <si>
-    <t>LP057154</t>
-  </si>
-  <si>
-    <t>LP057136</t>
-  </si>
-  <si>
-    <t>LP057122</t>
-  </si>
-  <si>
-    <t>LP057123</t>
-  </si>
-  <si>
-    <t>LP057138</t>
-  </si>
-  <si>
-    <t>LP057233</t>
-  </si>
-  <si>
-    <t>LP057172</t>
-  </si>
-  <si>
-    <t>LP057173</t>
-  </si>
-  <si>
-    <t>LP057175</t>
-  </si>
-  <si>
-    <t>LP057186</t>
-  </si>
-  <si>
-    <t>LP057163</t>
-  </si>
-  <si>
-    <t>LP057210</t>
-  </si>
-  <si>
-    <t>LP057212</t>
-  </si>
-  <si>
-    <t>LP057211</t>
-  </si>
-  <si>
-    <t>LP057208</t>
-  </si>
-  <si>
-    <t>LP057177</t>
-  </si>
-  <si>
-    <t>LP057180</t>
-  </si>
-  <si>
-    <t>LP057179</t>
-  </si>
-  <si>
-    <t>LP057405</t>
-  </si>
-  <si>
-    <t>LP057392</t>
-  </si>
-  <si>
-    <t>LP057391</t>
-  </si>
-  <si>
-    <t>LP057196</t>
-  </si>
-  <si>
-    <t>LP057293</t>
-  </si>
-  <si>
-    <t>LP057206</t>
-  </si>
-  <si>
-    <t>LP057205</t>
-  </si>
-  <si>
-    <t>LP057292</t>
-  </si>
-  <si>
-    <t>LP057207</t>
-  </si>
-  <si>
-    <t>LP057393</t>
-  </si>
-  <si>
-    <t>LP057482</t>
-  </si>
-  <si>
-    <t>LP057227</t>
-  </si>
-  <si>
-    <t>LP057229</t>
-  </si>
-  <si>
-    <t>LP057230</t>
-  </si>
-  <si>
-    <t>LP057231</t>
-  </si>
-  <si>
-    <t>LP057232</t>
-  </si>
-  <si>
-    <t>LP057316</t>
-  </si>
-  <si>
-    <t>LP057384</t>
-  </si>
-  <si>
-    <t>LP057304</t>
   </si>
 </sst>
 </file>
@@ -951,7 +954,7 @@
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -959,383 +962,509 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="B48">
         <v>2</v>
@@ -1343,7 +1472,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -1351,7 +1480,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="B50">
         <v>2</v>
@@ -1359,7 +1488,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -1367,7 +1496,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="B52">
         <v>2</v>
@@ -1375,7 +1504,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -1383,7 +1512,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -1391,7 +1520,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="B55">
         <v>2</v>
@@ -1399,7 +1528,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -1407,7 +1536,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -1415,7 +1544,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -1423,7 +1552,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -1431,7 +1560,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -1439,7 +1568,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -1447,7 +1576,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -1455,7 +1584,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -1463,7 +1592,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -1471,7 +1600,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -1479,7 +1608,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -1487,7 +1616,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -1495,7 +1624,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -1503,7 +1632,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -1511,7 +1640,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1519,7 +1648,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -1527,7 +1656,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -1535,7 +1664,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -1543,7 +1672,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -1551,7 +1680,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -1559,7 +1688,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -1567,7 +1696,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -1575,7 +1704,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -1583,7 +1712,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -1591,7 +1720,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -1599,7 +1728,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1607,7 +1736,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -1615,7 +1744,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -1623,7 +1752,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -1631,7 +1760,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -1639,7 +1768,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -1647,7 +1776,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -1655,7 +1784,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -1663,7 +1792,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -1671,7 +1800,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>155</v>
+        <v>92</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -1679,7 +1808,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -1687,7 +1816,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -1695,7 +1824,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -1703,7 +1832,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -1711,7 +1840,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -1719,7 +1848,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -1727,7 +1856,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -1735,7 +1864,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -1743,7 +1872,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -1751,7 +1880,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -1759,7 +1888,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -1767,7 +1896,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="B102">
         <v>2</v>
@@ -1775,7 +1904,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="B103">
         <v>2</v>
@@ -1783,7 +1912,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>169</v>
+        <v>106</v>
       </c>
       <c r="B104">
         <v>2</v>
@@ -1791,7 +1920,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
       <c r="B105">
         <v>2</v>
@@ -1799,7 +1928,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1807,7 +1936,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="B107">
         <v>2</v>
@@ -1815,7 +1944,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -1823,7 +1952,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="B109">
         <v>2</v>
@@ -1831,7 +1960,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -1839,7 +1968,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="B111">
         <v>2</v>
@@ -1847,7 +1976,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>177</v>
+        <v>114</v>
       </c>
       <c r="B112">
         <v>2</v>
@@ -1855,7 +1984,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="B113">
         <v>2</v>
@@ -1863,7 +1992,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="B114">
         <v>2</v>
@@ -1871,7 +2000,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>180</v>
+        <v>117</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -1879,7 +2008,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -1887,7 +2016,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="B117">
         <v>2</v>
@@ -1895,7 +2024,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>183</v>
+        <v>120</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -1903,7 +2032,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>184</v>
+        <v>121</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -1911,7 +2040,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>185</v>
+        <v>122</v>
       </c>
       <c r="B120">
         <v>2</v>
@@ -1919,7 +2048,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>186</v>
+        <v>123</v>
       </c>
       <c r="B121">
         <v>2</v>
@@ -1927,7 +2056,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="B122">
         <v>2</v>
@@ -1935,7 +2064,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="B123">
         <v>2</v>
@@ -1943,7 +2072,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -1951,7 +2080,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -1959,7 +2088,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -1967,7 +2096,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="B127">
         <v>2</v>
@@ -1975,7 +2104,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B128">
         <v>2</v>
@@ -1983,7 +2112,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="B129">
         <v>2</v>
@@ -1991,7 +2120,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>9</v>
+        <v>132</v>
       </c>
       <c r="B130">
         <v>2</v>
@@ -1999,7 +2128,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="B131">
         <v>2</v>
@@ -2007,7 +2136,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>134</v>
       </c>
       <c r="B132">
         <v>2</v>
@@ -2015,7 +2144,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2023,7 +2152,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="B134">
         <v>2</v>
@@ -2031,7 +2160,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="B135">
         <v>2</v>
@@ -2039,7 +2168,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="B136">
         <v>2</v>
@@ -2047,7 +2176,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="B137">
         <v>2</v>
@@ -2055,7 +2184,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="B138">
         <v>2</v>
@@ -2063,7 +2192,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="B139">
         <v>2</v>
@@ -2071,7 +2200,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="B140">
         <v>2</v>
@@ -2079,7 +2208,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="B141">
         <v>2</v>
@@ -2087,7 +2216,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="B142">
         <v>2</v>
@@ -2095,7 +2224,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2103,7 +2232,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2111,7 +2240,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="B145">
         <v>2</v>
@@ -2119,7 +2248,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="B146">
         <v>2</v>
@@ -2127,7 +2256,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="B147">
         <v>2</v>
@@ -2135,7 +2264,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="B148">
         <v>2</v>
@@ -2143,7 +2272,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>28</v>
+        <v>151</v>
       </c>
       <c r="B149">
         <v>2</v>
@@ -2151,7 +2280,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="B150">
         <v>2</v>
@@ -2159,7 +2288,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="B151">
         <v>2</v>
@@ -2167,7 +2296,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="B152">
         <v>2</v>
@@ -2175,7 +2304,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2183,7 +2312,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="B154">
         <v>2</v>
@@ -2191,7 +2320,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2199,7 +2328,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="B156">
         <v>2</v>
@@ -2207,7 +2336,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2215,7 +2344,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>37</v>
+        <v>160</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2223,7 +2352,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="B159">
         <v>2</v>
@@ -2231,7 +2360,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="B160">
         <v>2</v>
@@ -2239,7 +2368,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="B161">
         <v>2</v>
@@ -2247,7 +2376,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="B162">
         <v>2</v>
@@ -2255,7 +2384,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="B163">
         <v>2</v>
@@ -2263,7 +2392,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="B164">
         <v>2</v>
@@ -2271,7 +2400,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="B165">
         <v>2</v>
@@ -2279,7 +2408,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="B166">
         <v>2</v>
@@ -2287,7 +2416,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="B167">
         <v>2</v>
@@ -2295,7 +2424,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B168">
         <v>2</v>
@@ -2303,7 +2432,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="B169">
         <v>2</v>
@@ -2311,7 +2440,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
       <c r="B170">
         <v>2</v>
@@ -2319,7 +2448,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2327,7 +2456,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="B172">
         <v>2</v>
@@ -2335,7 +2464,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2343,7 +2472,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
       <c r="B174">
         <v>2</v>
@@ -2351,7 +2480,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="B175">
         <v>2</v>
@@ -2359,7 +2488,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="B176">
         <v>2</v>
@@ -2367,7 +2496,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2375,7 +2504,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="B178">
         <v>2</v>
@@ -2383,7 +2512,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="B179">
         <v>2</v>
@@ -2391,7 +2520,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="B180">
         <v>2</v>
@@ -2399,7 +2528,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="B181">
         <v>2</v>
@@ -2407,7 +2536,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="B182">
         <v>2</v>
@@ -2415,7 +2544,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="B183">
         <v>2</v>
@@ -2423,7 +2552,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2431,7 +2560,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>64</v>
+        <v>187</v>
       </c>
       <c r="B185">
         <v>2</v>
@@ -2439,7 +2568,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="B186">
         <v>2</v>

--- a/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoYesica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7FA8FC-E9DB-4E82-9067-F5FEF5FD9D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3F44BB-5918-4D07-8D3D-FA49B3F093D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="189">
   <si>
     <t>LPs</t>
   </si>
@@ -1437,6 +1437,9 @@
       <c r="B44">
         <v>2</v>
       </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -1445,6 +1448,9 @@
       <c r="B45">
         <v>1</v>
       </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -1453,6 +1459,9 @@
       <c r="B46">
         <v>2</v>
       </c>
+      <c r="C46" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -1461,6 +1470,9 @@
       <c r="B47">
         <v>2</v>
       </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1469,144 +1481,198 @@
       <c r="B48">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>57</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>58</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>59</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>62</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>65</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C64" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -1614,7 +1680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -1622,7 +1688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -1630,7 +1696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -1638,7 +1704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -1646,7 +1712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -1654,7 +1720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -1662,7 +1728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -1670,7 +1736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -1678,7 +1744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -1686,7 +1752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -1694,7 +1760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -1702,7 +1768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -1710,7 +1776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -1718,7 +1784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>82</v>
       </c>
